--- a/companies list.xlsx
+++ b/companies list.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tarun\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BehaviorLens_India\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981C6FD3-2AD1-4CD0-BCE8-5C2631473961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF34AE6-4AEA-45A9-A0F0-42F4138AAB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indian Apps Dataset" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="90">
   <si>
     <t>Category</t>
   </si>
@@ -64,33 +77,6 @@
     <t>https://www.swiggy.com</t>
   </si>
   <si>
-    <t>Gaming</t>
-  </si>
-  <si>
-    <t>PUBG: Battlegrounds</t>
-  </si>
-  <si>
-    <t>South Korea</t>
-  </si>
-  <si>
-    <t>https://pubg.com</t>
-  </si>
-  <si>
-    <t>Battle Royale Game</t>
-  </si>
-  <si>
-    <t>Battlegrounds Mobile India</t>
-  </si>
-  <si>
-    <t>India (Krafton)</t>
-  </si>
-  <si>
-    <t>https://www.battlegroundsmobileindia.com</t>
-  </si>
-  <si>
-    <t>Mobile Battle Royale Game</t>
-  </si>
-  <si>
     <t>E-Commerce</t>
   </si>
   <si>
@@ -106,9 +92,6 @@
     <t>Amazon India</t>
   </si>
   <si>
-    <t>India (Subsidiary of Amazon)</t>
-  </si>
-  <si>
     <t>https://www.amazon.in</t>
   </si>
   <si>
@@ -130,30 +113,18 @@
     <t>Fashion E-Commerce</t>
   </si>
   <si>
-    <t>FinTech</t>
-  </si>
-  <si>
     <t>Paytm</t>
   </si>
   <si>
     <t>Noida, India</t>
   </si>
   <si>
-    <t>https://www.paytm.com</t>
-  </si>
-  <si>
     <t>PhonePe</t>
   </si>
   <si>
     <t>https://www.phonepe.com</t>
   </si>
   <si>
-    <t>Google Pay (GPay)</t>
-  </si>
-  <si>
-    <t>India (Google)</t>
-  </si>
-  <si>
     <t>https://pay.google.com</t>
   </si>
   <si>
@@ -166,36 +137,21 @@
     <t>https://byjus.com</t>
   </si>
   <si>
-    <t>Online Education</t>
-  </si>
-  <si>
     <t>Unacademy</t>
   </si>
   <si>
     <t>https://unacademy.com</t>
   </si>
   <si>
-    <t>PhysicsWallah</t>
-  </si>
-  <si>
     <t>https://www.pw.live</t>
   </si>
   <si>
-    <t>Diital Payments</t>
-  </si>
-  <si>
     <t>Quick Commerce</t>
   </si>
   <si>
     <t>Blinkit</t>
   </si>
   <si>
-    <t>https://www.blinkit.com</t>
-  </si>
-  <si>
-    <t>10-Minute Delivery</t>
-  </si>
-  <si>
     <t>Zepto</t>
   </si>
   <si>
@@ -205,59 +161,155 @@
     <t>https://www.zeptonow.com</t>
   </si>
   <si>
-    <t>Social Media</t>
-  </si>
-  <si>
-    <t>Instagram</t>
-  </si>
-  <si>
-    <t>Menlo Park, USA</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com</t>
-  </si>
-  <si>
-    <t>Photo &amp; Video Sharing</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com</t>
-  </si>
-  <si>
-    <t>Social Networking</t>
-  </si>
-  <si>
-    <t>X (formerly Twitter)</t>
-  </si>
-  <si>
-    <t>San Francisco, USA</t>
-  </si>
-  <si>
-    <t>https://www.twitter.com</t>
-  </si>
-  <si>
-    <t>Microblogging Platform</t>
-  </si>
-  <si>
-    <t>YouTube</t>
-  </si>
-  <si>
-    <t>San Bruno, USA</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com</t>
-  </si>
-  <si>
-    <t>Video Sharing Platform</t>
+    <t>EatSure</t>
+  </si>
+  <si>
+    <t>https://www.eatsure.com</t>
+  </si>
+  <si>
+    <t>https://blinkit.com</t>
+  </si>
+  <si>
+    <t>Swiggy Instamart</t>
+  </si>
+  <si>
+    <t>https://www.swiggy.com/instamart</t>
+  </si>
+  <si>
+    <t>BigBasket</t>
+  </si>
+  <si>
+    <t>https://www.bigbasket.com</t>
+  </si>
+  <si>
+    <t>Online Grocery / Quick Commerce</t>
+  </si>
+  <si>
+    <t>JioMart</t>
+  </si>
+  <si>
+    <t>Navi Mumbai, India</t>
+  </si>
+  <si>
+    <t>https://www.jiomart.com</t>
+  </si>
+  <si>
+    <t>Online Grocery / E-Commerce</t>
+  </si>
+  <si>
+    <t>AJIO</t>
+  </si>
+  <si>
+    <t>https://www.ajio.com</t>
+  </si>
+  <si>
+    <t>Digital Payments / FinTech</t>
+  </si>
+  <si>
+    <t>Digital Payments</t>
+  </si>
+  <si>
+    <t>https://paytm.com</t>
+  </si>
+  <si>
+    <t>Google Pay India</t>
+  </si>
+  <si>
+    <t>MobiKwik</t>
+  </si>
+  <si>
+    <t>https://www.mobikwik.com</t>
+  </si>
+  <si>
+    <t>CRED</t>
+  </si>
+  <si>
+    <t>https://cred.club</t>
+  </si>
+  <si>
+    <t>FinTech / Credit Card Payments</t>
+  </si>
+  <si>
+    <t>Physics Wallah</t>
+  </si>
+  <si>
+    <t>Vedantu</t>
+  </si>
+  <si>
+    <t>https://www.vedantu.com</t>
+  </si>
+  <si>
+    <t>Ride-Hailing / Mobility</t>
+  </si>
+  <si>
+    <t>Rapido</t>
+  </si>
+  <si>
+    <t>https://www.rapido.bike</t>
+  </si>
+  <si>
+    <t>Bike Taxi / Ride-Hailing</t>
+  </si>
+  <si>
+    <t>Ola</t>
+  </si>
+  <si>
+    <t>https://www.olacabs.com</t>
+  </si>
+  <si>
+    <t>Ride-Hailing</t>
+  </si>
+  <si>
+    <t>Uber India</t>
+  </si>
+  <si>
+    <t>https://www.uber.com/in/en/</t>
+  </si>
+  <si>
+    <t>Travel / Transport Booking</t>
+  </si>
+  <si>
+    <t>MakeMyTrip</t>
+  </si>
+  <si>
+    <t>https://www.makemytrip.com</t>
+  </si>
+  <si>
+    <t>Online Travel Booking</t>
+  </si>
+  <si>
+    <t>redBus</t>
+  </si>
+  <si>
+    <t>https://www.redbus.in</t>
+  </si>
+  <si>
+    <t>Bus Ticket Booking</t>
+  </si>
+  <si>
+    <t>AbhiBus</t>
+  </si>
+  <si>
+    <t>Hyderabad, India</t>
+  </si>
+  <si>
+    <t>https://www.abhibus.com</t>
+  </si>
+  <si>
+    <t>EaseMyTrip</t>
+  </si>
+  <si>
+    <t>New Delhi, India</t>
+  </si>
+  <si>
+    <t>https://www.easemytrip.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,25 +318,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -296,32 +351,36 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -622,10 +681,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.36328125" customWidth="1"/>
     <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
@@ -634,402 +693,640 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>2008</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="4"/>
-      <c r="B3" t="s">
+      <c r="A3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>2014</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2020</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2013</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2021</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2020</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2011</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="11" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2013</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C4">
+      <c r="C11" s="3">
+        <v>2007</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2015</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2007</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2016</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2015</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2010</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="3">
         <v>2017</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5">
-        <v>2021</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6">
-        <v>2007</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="4"/>
-      <c r="B7" t="s">
+      <c r="D17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2009</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2020</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C7">
+      <c r="E20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2015</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2011</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2011</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2015</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2010</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="3">
         <v>2013</v>
       </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="4"/>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>2015</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="4"/>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9">
-        <v>2007</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="11" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2010</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4"/>
-      <c r="B11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2015</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4"/>
-      <c r="B12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13">
-        <v>2011</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="3"/>
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14">
-        <v>2015</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="3"/>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15">
-        <v>2020</v>
-      </c>
-      <c r="D15" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="6">
-        <v>2021</v>
-      </c>
-      <c r="D16" s="6" t="s">
+      <c r="D26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="3">
+        <v>2000</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="8"/>
-      <c r="B17" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="6">
-        <v>2021</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="9">
-        <v>2010</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="3"/>
-      <c r="B19" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="9">
-        <v>2004</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
-      <c r="B20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="9">
+      <c r="E27" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="3">
         <v>2006</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="3"/>
-      <c r="B21" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="9">
-        <v>2005</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>76</v>
+      <c r="D28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="3">
+        <v>2008</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="3">
+        <v>2008</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="F10:F12"/>
-  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://www.zomato.com/" xr:uid="{49F6DFF0-2317-49A1-AF8C-DFFF7B2D3120}"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://www.swiggy.com/" xr:uid="{B010F926-571A-453A-8F5D-13C27AEBE00F}"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://www.eatsure.com/" xr:uid="{D7CD7533-9B8F-4A9A-A7CE-A3F3E33FBA59}"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://blinkit.com/" xr:uid="{3BFC252C-A851-4EB9-B78F-707F477E341A}"/>
+    <hyperlink ref="E6" r:id="rId5" display="https://www.zeptonow.com/" xr:uid="{09BE0DF5-8F6B-4C4F-A3DC-FB99F66E6DF9}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{BAB2305B-2219-412A-A6E6-B3C9D5D9C90C}"/>
+    <hyperlink ref="E8" r:id="rId7" display="https://www.bigbasket.com/" xr:uid="{FE59EA35-9013-4B9B-924E-7FDACF6682A1}"/>
+    <hyperlink ref="E9" r:id="rId8" display="https://www.jiomart.com/" xr:uid="{34AB4C37-9971-439C-B6C4-12F305A4B422}"/>
+    <hyperlink ref="E10" r:id="rId9" display="https://www.amazon.in/" xr:uid="{1A7E7102-7A84-46E7-85E8-68EEEA0D6BB1}"/>
+    <hyperlink ref="E11" r:id="rId10" display="https://www.flipkart.com/" xr:uid="{F5C5E35B-A787-452C-B183-F608807D2BBB}"/>
+    <hyperlink ref="E12" r:id="rId11" display="https://www.meesho.com/" xr:uid="{0045C774-2A9C-4507-B7D0-4D8EF16EBC0F}"/>
+    <hyperlink ref="E13" r:id="rId12" display="https://www.myntra.com/" xr:uid="{C2A5486A-DB81-4916-9599-70284DADD5A8}"/>
+    <hyperlink ref="E14" r:id="rId13" display="https://www.ajio.com/" xr:uid="{4E6B94C5-FBA2-47D1-8B52-ABC4F2A8C5A7}"/>
+    <hyperlink ref="E15" r:id="rId14" display="https://www.phonepe.com/" xr:uid="{49972D68-EDAB-4C29-BFF5-B285496361A9}"/>
+    <hyperlink ref="E16" r:id="rId15" display="https://paytm.com/" xr:uid="{C2168BBB-8F3B-4160-8EA0-36E90D1EE043}"/>
+    <hyperlink ref="E17" r:id="rId16" display="https://pay.google.com/" xr:uid="{A5C22F16-C88C-4C5B-ABFC-0A4310145C3B}"/>
+    <hyperlink ref="E18" r:id="rId17" display="https://www.mobikwik.com/" xr:uid="{8492A64C-B695-4677-8D2A-6EE1B43E10E9}"/>
+    <hyperlink ref="E19" r:id="rId18" display="https://cred.club/" xr:uid="{4513757F-9D46-42F5-9CDA-69868D9CB362}"/>
+    <hyperlink ref="E20" r:id="rId19" display="https://www.pw.live/" xr:uid="{8C4CA09E-5305-4DB1-A419-4E6D7538BA44}"/>
+    <hyperlink ref="E21" r:id="rId20" display="https://unacademy.com/" xr:uid="{2CFC22BE-1FF1-4B46-825E-A67247A6E35C}"/>
+    <hyperlink ref="E22" r:id="rId21" display="https://byjus.com/" xr:uid="{E13A77A7-5956-4F61-9DFF-E17134A1E5B9}"/>
+    <hyperlink ref="E23" r:id="rId22" display="https://www.vedantu.com/" xr:uid="{0C4AED10-8B4F-43C5-9311-AFDB20A84A4A}"/>
+    <hyperlink ref="E24" r:id="rId23" display="https://www.rapido.bike/" xr:uid="{8D3003E6-0B1B-451E-8728-A29EE175BDC4}"/>
+    <hyperlink ref="E25" r:id="rId24" display="https://www.olacabs.com/" xr:uid="{57D119AB-7BCB-48A4-A086-49B886AE4D4C}"/>
+    <hyperlink ref="E26" r:id="rId25" xr:uid="{CAF63DBC-B98E-42C2-8E08-BC038B04174F}"/>
+    <hyperlink ref="E27" r:id="rId26" display="https://www.makemytrip.com/" xr:uid="{D064EC89-26E0-4185-9E92-3C9D9B1C0D08}"/>
+    <hyperlink ref="E28" r:id="rId27" display="https://www.redbus.in/" xr:uid="{8C1B97E8-8254-442A-B985-CAAF60EFC361}"/>
+    <hyperlink ref="E29" r:id="rId28" display="https://www.abhibus.com/" xr:uid="{B91F61B9-BDED-4BA9-B924-4AE6C9552270}"/>
+    <hyperlink ref="E30" r:id="rId29" display="https://www.easemytrip.com/" xr:uid="{4A22621F-8724-4588-8026-CD5BBF8780F3}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId30"/>
 </worksheet>
 </file>